--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0003T0006Z000C1N43_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0003T0006Z000C1N43_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,10 +486,10 @@
         <v>15.9805349908863</v>
       </c>
       <c r="E2" t="n">
-        <v>3.572548043936101</v>
+        <v>3.296831850465457</v>
       </c>
       <c r="F2" t="n">
-        <v>3.177365907967219</v>
+        <v>3.008829120924949</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -518,10 +518,10 @@
         <v>9.625803174951864</v>
       </c>
       <c r="E3" t="n">
-        <v>3.572548043936101</v>
+        <v>3.296831850465457</v>
       </c>
       <c r="F3" t="n">
-        <v>3.177365907967219</v>
+        <v>3.008829120924949</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -529,6 +529,38 @@
         </is>
       </c>
       <c r="H3" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>W0029F0003T0006Z000C1N43.png</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>9.445482730077924</v>
+      </c>
+      <c r="D4" t="n">
+        <v>9.570248620577027</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3.296831850465457</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3.008829120924949</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>T7604</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0003T0006Z000C1N43_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0003T0006Z000C1N43_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>16.27711846037668</v>
+        <v>2.645031749811211</v>
       </c>
       <c r="D2" t="n">
-        <v>15.9805349908863</v>
+        <v>2.596836936019024</v>
       </c>
       <c r="E2" t="n">
-        <v>3.296831850465457</v>
+        <v>0.5357351757006368</v>
       </c>
       <c r="F2" t="n">
-        <v>3.008829120924949</v>
+        <v>0.4889347321503044</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>9.132022372504482</v>
+        <v>1.483953635531978</v>
       </c>
       <c r="D3" t="n">
-        <v>9.625803174951864</v>
+        <v>1.564193015929678</v>
       </c>
       <c r="E3" t="n">
-        <v>3.296831850465457</v>
+        <v>0.5357351757006368</v>
       </c>
       <c r="F3" t="n">
-        <v>3.008829120924949</v>
+        <v>0.4889347321503044</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>9.445482730077924</v>
+        <v>1.534890943637663</v>
       </c>
       <c r="D4" t="n">
-        <v>9.570248620577027</v>
+        <v>1.555165400843767</v>
       </c>
       <c r="E4" t="n">
-        <v>3.296831850465457</v>
+        <v>0.5357351757006368</v>
       </c>
       <c r="F4" t="n">
-        <v>3.008829120924949</v>
+        <v>0.4889347321503044</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
